--- a/input_updated.xlsx
+++ b/input_updated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,17 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>latest_status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest_time</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delivered</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest_status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>latest_time</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -446,40 +446,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>IBR5765886793985658886</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>运单签收</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>2026-02-07 07:33</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.13下单-1.17义乌入库-2.7送达</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>IBR5765921754683772934</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-06 13:26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.20下单-1.28义乌入库-2.6送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IBR5765921792373002246</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-10 12:56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.20下单-1.28义乌入库-2.10送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IBR5765921845580959750</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:31</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.21下单-1.28义乌入库-2.10送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IBR5765921893596958726</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-11 10:54</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.21下单-1.28义乌入库-2.11送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IBR5765922112847187974</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-02-09 11:18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.20下单-1.28义乌入库-2.9送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IBR5764720910053184518</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>运单已确认</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-02-11 17:53</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.3下单-2.11义乌入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IBR5764720910053250054</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>运单已确认</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-02-11 17:53</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2.3下单-2.11义乌入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IBR5764720910053315590</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>运单已确认</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-02-11 17:53</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2.3下单-2.11义乌入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IBR5764720910053381126</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>运单已确认</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-02-11 17:53</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2.3下单-2.11义乌入库</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
